--- a/KatalonData/IVT/IVT_Login.xlsx
+++ b/KatalonData/IVT/IVT_Login.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="27">
   <si>
     <t>Result</t>
   </si>
@@ -237,6 +237,39 @@
   </si>
   <si>
     <t>Mon Sep 07 23:44:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 08 21:08:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 10 20:02:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 10 22:20:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Thu Sep 10 22:26:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 11 10:16:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 11 21:32:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 11 21:43:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 15 15:15:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 15 20:29:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 15 21:54:18 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -715,7 +748,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>13</v>

--- a/KatalonData/IVT/IVT_Login.xlsx
+++ b/KatalonData/IVT/IVT_Login.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="29">
   <si>
     <t>Result</t>
   </si>
@@ -270,6 +270,12 @@
   </si>
   <si>
     <t>Tue Sep 15 21:54:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 16 18:52:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 16 21:41:32 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -748,7 +754,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>13</v>

--- a/KatalonData/IVT/IVT_Login.xlsx
+++ b/KatalonData/IVT/IVT_Login.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="31">
   <si>
     <t>Result</t>
   </si>
@@ -276,6 +276,12 @@
   </si>
   <si>
     <t>Wed Sep 16 21:41:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 17 17:24:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 17 18:02:30 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -754,7 +760,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>13</v>

--- a/KatalonData/IVT/IVT_Login.xlsx
+++ b/KatalonData/IVT/IVT_Login.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="37">
   <si>
     <t>Result</t>
   </si>
@@ -285,6 +285,21 @@
   </si>
   <si>
     <t>Fri Sep 18 12:55:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Sep 28 17:35:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 29 12:05:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 29 20:02:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:31:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:35:45 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -763,7 +778,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>13</v>

--- a/KatalonData/IVT/IVT_Login.xlsx
+++ b/KatalonData/IVT/IVT_Login.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="41">
   <si>
     <t>Result</t>
   </si>
@@ -300,6 +300,18 @@
   </si>
   <si>
     <t>Thu Oct 01 00:35:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 16:01:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 16:02:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 16:22:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 20:43:00 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -778,7 +790,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>13</v>

--- a/KatalonData/IVT/IVT_Login.xlsx
+++ b/KatalonData/IVT/IVT_Login.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\IVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BC0387-6D1A-448D-A767-3DD89AA51E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{617DAD01-5464-4F19-90AB-D07EB123046A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
     <sheet name="Submit_SameJson" sheetId="6" r:id="rId1"/>
-    <sheet name="Submit_ChangedAppId" sheetId="3" r:id="rId2"/>
-    <sheet name="Submit_ChangedParcel" sheetId="1" r:id="rId3"/>
-    <sheet name="Submit_ChangedAddress" sheetId="4" r:id="rId4"/>
-    <sheet name="Submit_ChangedCustom" sheetId="5" r:id="rId5"/>
+    <sheet name="Submit_ChangedCAN" sheetId="7" r:id="rId2"/>
+    <sheet name="Submit_ChangedAppId" sheetId="3" r:id="rId3"/>
+    <sheet name="Submit_ChangedParcel" sheetId="1" r:id="rId4"/>
+    <sheet name="Submit_ChangedAddress" sheetId="4" r:id="rId5"/>
+    <sheet name="Submit_ChangedCustom" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="53">
   <si>
     <t>Result</t>
   </si>
@@ -236,82 +237,593 @@
 }</t>
   </si>
   <si>
-    <t>Mon Sep 07 23:44:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Sep 08 21:08:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 10 20:02:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 10 22:20:51 IST 2026</t>
+    <t>Thu Oct 08 20:43:00 IST 2026</t>
+  </si>
+  <si>
+    <t>ErrorMessage</t>
+  </si>
+  <si>
+    <t>Submit Request:
+applicationId- will always be 1024.
+remittanceId- will always be unique(alphanumeric).
+CAN should accept- 1 character numeric</t>
+  </si>
+  <si>
+    <t>Submit Request:
+applicationId- will always be 1024.
+remittanceId- will always be unique(alphanumeric).
+CAN should accept- 1 character albhabetic</t>
+  </si>
+  <si>
+    <t>Submit Request:
+applicationId- will always be 1024.
+remittanceId- will always be unique(alphanumeric).
+CAN should accept- 50 character alphanumeric</t>
+  </si>
+  <si>
+    <t>Submit Request:
+applicationId- will always be 1024.
+remittanceId- will always be unique(alphanumeric).
+CAN should accept- with underscore (_)</t>
+  </si>
+  <si>
+    <t>Submit Request:
+applicationId- will always be 1024.
+remittanceId- will always be unique(alphanumeric).
+CAN should accept- with pipe (|)</t>
+  </si>
+  <si>
+    <t>Submit Request:
+applicationId- will always be 1024.
+remittanceId- will always be unique(alphanumeric).
+CAN should reject- more than 50 character alphanumeric</t>
+  </si>
+  <si>
+    <t>Submit Request:
+applicationId- will always be 1024.
+remittanceId- will always be unique(alphanumeric).
+CAN should reject- with space</t>
+  </si>
+  <si>
+    <t>Submit Request:
+applicationId- will always be 1024.
+remittanceId- will always be unique(alphanumeric).
+CAN should reject- speacial characters other tnan underscore (_) 
+pipe (|)</t>
+  </si>
+  <si>
+    <t>{
+  "amount": 20.00,
+  "clientAccountNumber": "1",
+  "applicationId": "1024",
+  "remittanceId": "ABC12329",
+  "cashierName": "Cashier1",
+  "pinpadName": "Counter-001",
+  "parcel": [
+    ["1", "2", "4"],
+    ["1", "2", "3"],
+    ["1", "2", "3"]
+  ],
+  "billingAddress": {
+    "firstName": "Jane",
+    "lastName": "Doe",
+    "companyName": "ABC Company",
+    "address": "123 Main St",
+    "address2": "Apt 5",
+    "postalCode": "22201",
+    "city": "Arlington",
+    "state": "VA",
+    "country": "USA",
+    "phone": "111-222-3333",
+    "email": "jane@email.com"
+  },
+  "customData": {
+    "user_defined_1": "value 1",
+    "user_defined_2": "value 2",
+    "user_defined_3": "value 3",
+    "user_defined_4": "value 4",
+    "user_defined_5": "value 5",
+    "user_defined_6": "value 6",
+    "user_defined_7": "value 7",
+    "user_defined_8": "value 8",
+    "user_defined_9": "value 9",
+    "user_defined_10": "value 10"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "amount": 20.00,
+  "clientAccountNumber": "A",
+  "applicationId": "1024",
+  "remittanceId": "ABC12329",
+  "cashierName": "Cashier1",
+  "pinpadName": "Counter-001",
+  "parcel": [
+    ["1", "2", "4"],
+    ["1", "2", "3"],
+    ["1", "2", "3"]
+  ],
+  "billingAddress": {
+    "firstName": "Jane",
+    "lastName": "Doe",
+    "companyName": "ABC Company",
+    "address": "123 Main St",
+    "address2": "Apt 5",
+    "postalCode": "22201",
+    "city": "Arlington",
+    "state": "VA",
+    "country": "USA",
+    "phone": "111-222-3333",
+    "email": "jane@email.com"
+  },
+  "customData": {
+    "user_defined_1": "value 1",
+    "user_defined_2": "value 2",
+    "user_defined_3": "value 3",
+    "user_defined_4": "value 4",
+    "user_defined_5": "value 5",
+    "user_defined_6": "value 6",
+    "user_defined_7": "value 7",
+    "user_defined_8": "value 8",
+    "user_defined_9": "value 9",
+    "user_defined_10": "value 10"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 21:38:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 21:38:48 IST 2026</t>
+  </si>
+  <si>
+    <t>{
+  "amount": 20.00,
+  "clientAccountNumber": "abcdasakaskdknckcnksdnc1212121nnlzmclsmcmcsm12112m",
+  "applicationId": "1024",
+  "remittanceId": "ABC12329",
+  "cashierName": "Cashier1",
+  "pinpadName": "Counter-001",
+  "parcel": [
+    ["1", "2", "4"],
+    ["1", "2", "3"],
+    ["1", "2", "3"]
+  ],
+  "billingAddress": {
+    "firstName": "Jane",
+    "lastName": "Doe",
+    "companyName": "ABC Company",
+    "address": "123 Main St",
+    "address2": "Apt 5",
+    "postalCode": "22201",
+    "city": "Arlington",
+    "state": "VA",
+    "country": "USA",
+    "phone": "111-222-3333",
+    "email": "jane@email.com"
+  },
+  "customData": {
+    "user_defined_1": "value 1",
+    "user_defined_2": "value 2",
+    "user_defined_3": "value 3",
+    "user_defined_4": "value 4",
+    "user_defined_5": "value 5",
+    "user_defined_6": "value 6",
+    "user_defined_7": "value 7",
+    "user_defined_8": "value 8",
+    "user_defined_9": "value 9",
+    "user_defined_10": "value 10"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "amount": 20.00,
+  "clientAccountNumber": "abcdasakaskdknckcnksdnc1212121nnlzmclsmcmcsm12112m33",
+  "applicationId": "1024",
+  "remittanceId": "ABC12329",
+  "cashierName": "Cashier1",
+  "pinpadName": "Counter-001",
+  "parcel": [
+    ["1", "2", "4"],
+    ["1", "2", "3"],
+    ["1", "2", "3"]
+  ],
+  "billingAddress": {
+    "firstName": "Jane",
+    "lastName": "Doe",
+    "companyName": "ABC Company",
+    "address": "123 Main St",
+    "address2": "Apt 5",
+    "postalCode": "22201",
+    "city": "Arlington",
+    "state": "VA",
+    "country": "USA",
+    "phone": "111-222-3333",
+    "email": "jane@email.com"
+  },
+  "customData": {
+    "user_defined_1": "value 1",
+    "user_defined_2": "value 2",
+    "user_defined_3": "value 3",
+    "user_defined_4": "value 4",
+    "user_defined_5": "value 5",
+    "user_defined_6": "value 6",
+    "user_defined_7": "value 7",
+    "user_defined_8": "value 8",
+    "user_defined_9": "value 9",
+    "user_defined_10": "value 10"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "amount": 20.00,
+  "clientAccountNumber": "12ab_",
+  "applicationId": "1024",
+  "remittanceId": "ABC12329",
+  "cashierName": "Cashier1",
+  "pinpadName": "Counter-001",
+  "parcel": [
+    ["1", "2", "4"],
+    ["1", "2", "3"],
+    ["1", "2", "3"]
+  ],
+  "billingAddress": {
+    "firstName": "Jane",
+    "lastName": "Doe",
+    "companyName": "ABC Company",
+    "address": "123 Main St",
+    "address2": "Apt 5",
+    "postalCode": "22201",
+    "city": "Arlington",
+    "state": "VA",
+    "country": "USA",
+    "phone": "111-222-3333",
+    "email": "jane@email.com"
+  },
+  "customData": {
+    "user_defined_1": "value 1",
+    "user_defined_2": "value 2",
+    "user_defined_3": "value 3",
+    "user_defined_4": "value 4",
+    "user_defined_5": "value 5",
+    "user_defined_6": "value 6",
+    "user_defined_7": "value 7",
+    "user_defined_8": "value 8",
+    "user_defined_9": "value 9",
+    "user_defined_10": "value 10"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "amount": 20.00,
+  "clientAccountNumber": "123|a",
+  "applicationId": "1024",
+  "remittanceId": "ABC12329",
+  "cashierName": "Cashier1",
+  "pinpadName": "Counter-001",
+  "parcel": [
+    ["1", "2", "4"],
+    ["1", "2", "3"],
+    ["1", "2", "3"]
+  ],
+  "billingAddress": {
+    "firstName": "Jane",
+    "lastName": "Doe",
+    "companyName": "ABC Company",
+    "address": "123 Main St",
+    "address2": "Apt 5",
+    "postalCode": "22201",
+    "city": "Arlington",
+    "state": "VA",
+    "country": "USA",
+    "phone": "111-222-3333",
+    "email": "jane@email.com"
+  },
+  "customData": {
+    "user_defined_1": "value 1",
+    "user_defined_2": "value 2",
+    "user_defined_3": "value 3",
+    "user_defined_4": "value 4",
+    "user_defined_5": "value 5",
+    "user_defined_6": "value 6",
+    "user_defined_7": "value 7",
+    "user_defined_8": "value 8",
+    "user_defined_9": "value 9",
+    "user_defined_10": "value 10"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Submit Request:
+applicationId- will always be 1024.
+remittanceId- will always be unique(alphanumeric).
+CAN should accept- with underscore (_) &amp; pipe (|)</t>
+  </si>
+  <si>
+    <t>{
+  "amount": 20.00,
+  "clientAccountNumber": "_123|",
+  "applicationId": "1024",
+  "remittanceId": "ABC12329",
+  "cashierName": "Cashier1",
+  "pinpadName": "Counter-001",
+  "parcel": [
+    ["1", "2", "4"],
+    ["1", "2", "3"],
+    ["1", "2", "3"]
+  ],
+  "billingAddress": {
+    "firstName": "Jane",
+    "lastName": "Doe",
+    "companyName": "ABC Company",
+    "address": "123 Main St",
+    "address2": "Apt 5",
+    "postalCode": "22201",
+    "city": "Arlington",
+    "state": "VA",
+    "country": "USA",
+    "phone": "111-222-3333",
+    "email": "jane@email.com"
+  },
+  "customData": {
+    "user_defined_1": "value 1",
+    "user_defined_2": "value 2",
+    "user_defined_3": "value 3",
+    "user_defined_4": "value 4",
+    "user_defined_5": "value 5",
+    "user_defined_6": "value 6",
+    "user_defined_7": "value 7",
+    "user_defined_8": "value 8",
+    "user_defined_9": "value 9",
+    "user_defined_10": "value 10"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "amount": 20.00,
+  "clientAccountNumber": "",
+  "applicationId": "1024",
+  "remittanceId": "ABC12329",
+  "cashierName": "Cashier1",
+  "pinpadName": "Counter-001",
+  "parcel": [
+    ["1", "2", "4"],
+    ["1", "2", "3"],
+    ["1", "2", "3"]
+  ],
+  "billingAddress": {
+    "firstName": "Jane",
+    "lastName": "Doe",
+    "companyName": "ABC Company",
+    "address": "123 Main St",
+    "address2": "Apt 5",
+    "postalCode": "22201",
+    "city": "Arlington",
+    "state": "VA",
+    "country": "USA",
+    "phone": "111-222-3333",
+    "email": "jane@email.com"
+  },
+  "customData": {
+    "user_defined_1": "value 1",
+    "user_defined_2": "value 2",
+    "user_defined_3": "value 3",
+    "user_defined_4": "value 4",
+    "user_defined_5": "value 5",
+    "user_defined_6": "value 6",
+    "user_defined_7": "value 7",
+    "user_defined_8": "value 8",
+    "user_defined_9": "value 9",
+    "user_defined_10": "value 10"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "amount": 20.00,
+  "clientAccountNumber": " 123456",
+  "applicationId": "1024",
+  "remittanceId": "ABC12329",
+  "cashierName": "Cashier1",
+  "pinpadName": "Counter-001",
+  "parcel": [
+    ["1", "2", "4"],
+    ["1", "2", "3"],
+    ["1", "2", "3"]
+  ],
+  "billingAddress": {
+    "firstName": "Jane",
+    "lastName": "Doe",
+    "companyName": "ABC Company",
+    "address": "123 Main St",
+    "address2": "Apt 5",
+    "postalCode": "22201",
+    "city": "Arlington",
+    "state": "VA",
+    "country": "USA",
+    "phone": "111-222-3333",
+    "email": "jane@email.com"
+  },
+  "customData": {
+    "user_defined_1": "value 1",
+    "user_defined_2": "value 2",
+    "user_defined_3": "value 3",
+    "user_defined_4": "value 4",
+    "user_defined_5": "value 5",
+    "user_defined_6": "value 6",
+    "user_defined_7": "value 7",
+    "user_defined_8": "value 8",
+    "user_defined_9": "value 9",
+    "user_defined_10": "value 10"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "amount": 20.00,
+  "clientAccountNumber": "123456 ",
+  "applicationId": "1024",
+  "remittanceId": "ABC12329",
+  "cashierName": "Cashier1",
+  "pinpadName": "Counter-001",
+  "parcel": [
+    ["1", "2", "4"],
+    ["1", "2", "3"],
+    ["1", "2", "3"]
+  ],
+  "billingAddress": {
+    "firstName": "Jane",
+    "lastName": "Doe",
+    "companyName": "ABC Company",
+    "address": "123 Main St",
+    "address2": "Apt 5",
+    "postalCode": "22201",
+    "city": "Arlington",
+    "state": "VA",
+    "country": "USA",
+    "phone": "111-222-3333",
+    "email": "jane@email.com"
+  },
+  "customData": {
+    "user_defined_1": "value 1",
+    "user_defined_2": "value 2",
+    "user_defined_3": "value 3",
+    "user_defined_4": "value 4",
+    "user_defined_5": "value 5",
+    "user_defined_6": "value 6",
+    "user_defined_7": "value 7",
+    "user_defined_8": "value 8",
+    "user_defined_9": "value 9",
+    "user_defined_10": "value 10"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "amount": 20.00,
+  "clientAccountNumber": "1 23456",
+  "applicationId": "1024",
+  "remittanceId": "ABC12329",
+  "cashierName": "Cashier1",
+  "pinpadName": "Counter-001",
+  "parcel": [
+    ["1", "2", "4"],
+    ["1", "2", "3"],
+    ["1", "2", "3"]
+  ],
+  "billingAddress": {
+    "firstName": "Jane",
+    "lastName": "Doe",
+    "companyName": "ABC Company",
+    "address": "123 Main St",
+    "address2": "Apt 5",
+    "postalCode": "22201",
+    "city": "Arlington",
+    "state": "VA",
+    "country": "USA",
+    "phone": "111-222-3333",
+    "email": "jane@email.com"
+  },
+  "customData": {
+    "user_defined_1": "value 1",
+    "user_defined_2": "value 2",
+    "user_defined_3": "value 3",
+    "user_defined_4": "value 4",
+    "user_defined_5": "value 5",
+    "user_defined_6": "value 6",
+    "user_defined_7": "value 7",
+    "user_defined_8": "value 8",
+    "user_defined_9": "value 9",
+    "user_defined_10": "value 10"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "amount": 20.00,
+  "clientAccountNumber": "@123456*#",
+  "applicationId": "1024",
+  "remittanceId": "ABC12329",
+  "cashierName": "Cashier1",
+  "pinpadName": "Counter-001",
+  "parcel": [
+    ["1", "2", "4"],
+    ["1", "2", "3"],
+    ["1", "2", "3"]
+  ],
+  "billingAddress": {
+    "firstName": "Jane",
+    "lastName": "Doe",
+    "companyName": "ABC Company",
+    "address": "123 Main St",
+    "address2": "Apt 5",
+    "postalCode": "22201",
+    "city": "Arlington",
+    "state": "VA",
+    "country": "USA",
+    "phone": "111-222-3333",
+    "email": "jane@email.com"
+  },
+  "customData": {
+    "user_defined_1": "value 1",
+    "user_defined_2": "value 2",
+    "user_defined_3": "value 3",
+    "user_defined_4": "value 4",
+    "user_defined_5": "value 5",
+    "user_defined_6": "value 6",
+    "user_defined_7": "value 7",
+    "user_defined_8": "value 8",
+    "user_defined_9": "value 9",
+    "user_defined_10": "value 10"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 21:46:28 IST 2026</t>
   </si>
   <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>Thu Sep 10 22:26:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 11 10:16:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 11 21:32:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 11 21:43:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Sep 15 15:15:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Sep 15 20:29:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Sep 15 21:54:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Sep 16 18:52:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Sep 16 21:41:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 17 17:24:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 17 18:02:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 18 12:55:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Sep 28 17:35:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Sep 29 12:05:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Sep 29 20:02:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Oct 01 00:31:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Oct 01 00:35:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Oct 08 16:01:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Oct 08 16:02:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Oct 08 16:22:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Oct 08 20:43:00 IST 2026</t>
+    <t>Fri Oct 16 21:46:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 21:47:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 21:47:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 21:47:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 21:48:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 21:48:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 21:48:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 21:49:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 21:49:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Submit Request:
+applicationId- will always be 1024.
+remittanceId- will always be unique(alphanumeric).
+CAN should accept- null when CAN is not mandatory in VPOC</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 22:12:25 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -790,7 +1302,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>13</v>
@@ -832,6 +1344,289 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{529155BE-7EEA-4500-B814-3179D0D23A12}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="7" width="25.7265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="4" width="20.81640625" collapsed="true"/>
+    <col min="8" max="16384" style="4" width="8.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="3" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s" s="7">
+        <v>50</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4237FBEF-0E43-4D7C-A492-096F026631EA}">
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -914,7 +1709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -993,7 +1788,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825776FB-CEF4-435E-8470-EFDD60A698DF}">
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -1071,7 +1866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B2BBE81-9849-406E-A59D-BAB233FD5CD1}">
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
